--- a/agent_runs/manjidiwang/episodes/ep20/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep20/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>病房逼签（，总时长：12秒，镜头数：5个）</t>
+          <t>病房逼签</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>扬手威胁（，总时长：10秒，镜头数：4个）</t>
+          <t>扬手威胁</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>折腕制止（，总时长：11秒，镜头数：4个）</t>
+          <t>折腕制止</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>踹飞保镖（，总时长：12秒，镜头数：4个）</t>
+          <t>踹飞保镖</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>狼狈逃窜（，总时长：10秒，镜头数：4个）</t>
+          <t>狼狈逃窜</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>招标阴招（，总时长：10秒，镜头数：5个）</t>
+          <t>招标阴招</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>削苹果谈底牌（，总时长：14秒，镜头数：6个）</t>
+          <t>削苹果谈底牌</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>合伙人并肩（，总时长：15秒，镜头数：5个）</t>
+          <t>合伙人并肩</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
